--- a/output_excel/14944161.xlsx
+++ b/output_excel/14944161.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>P5 | CONEX. | P4-30 | C12X600112,5KVAB4A112,5KVABF-A | BT | BF-A | S143112,5KVA1AF(1) | 30K | 1x3x70(70)AX | 112,5KVA | 551412 | TX10 | TX10 | S145 | BF-A | C12X600112,5KVAB2F112,5KVAM3F | 21M | BF-A</t>
+          <t>CONEX. | BT | C12X600112,5KVAB4A112,5KVABF-A | BF-A | S143112,5KVA1AF(1) | 2 | 1x3x70(70)AX | 3 | TX10 | 551412 | TX10 | S145 | BF-A | C12X600112,5KVAB2F112,5KVAM3F | 21M | 14944166 | BF-A</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -620,7 +620,7 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>V4-5 | 9.26M | 30K | 21M | 37M | BF-A</t>
+          <t>9.26M | 30K | 21M | 37M | 551412 | 1x3x70(70)AX | BF-A | BF-A</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
@@ -657,27 +657,19 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>P4-30 | CONEX. | 112,5KVA | S145 | TX10 | C12X600112,5KVAB2F112,5KVAM3F | BT | P5 | 14944166 | BF-A | 1x3x70(70)AX | BF-A | 21M | 400816F | TX10 | C10x300,B1M,SMTG | C12X600112,5KVAB4A112,5KVABF-A</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>(DCIM) | GD | 4008661 | B1F | BT | ANCORAR | ANCORAR | XX | 1 | BT | CABOS | 112,5KVA | AVENIDA | CCO</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -718,11 +710,11 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>P31 | XX | GD | 4008661 | BT | (DCIM) | B1F | 112,5KVA | X63X51260(5708)A5X | B4F | C10X300112,5KVAS145 | ANCORAR | Q/R | 400816F | ANCORAR | ANCORAR | TX10 | 112,5KVA | CCO | 112,5KVA | BT | CABOS | AVENIDA | 112,5KVA | (DCIM) | BF-A | 84M | 112,5KVA | DCO</t>
+          <t>XX | GD | 4008661 | BT | (DCIM) | B1F | 1 | X63X51260(5708)A5X | B4F | C10X300112,5KVAS145</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -746,24 +738,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>V2-3</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42.77M</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>P2 | 175ET005296879 | 656529 | P1-11 | ETAPA | V1-2 | MX | 37,5KVA</t>
+          <t>X63X51260(5708)A5X | 1 | BT | V2-3</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -792,31 +788,23 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>P1-11</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>MX | P1-11 | 112,5KVA | TX10 | 175ET005296879 | C10X600112,5KVAET4A112,5KVAS144-2 | 400816F | ANCORAR | BF-A | 50KVA | ANCORAR | 656529 | 28M | B1F | 15KV_1F1(A) | (DCIM) | 37,5KVA112,5KVA112,5KVA | 15KV_1F1(A) | V1-9 | 37,5KVA112,5KVA112,5KVA | FERRAGEM | ANCORAR | M1M | 15KV_1L(C) | 6G | V1-2 | 35112,5KVA5M | ANCORAR</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>ETAPA | 7 | 175ET005296879 | 656529 | BF-A | 14944160 | BF-A</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -841,23 +829,23 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>V1-9</t>
+          <t>V1-2</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28m</t>
+          <t>32.2M</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>400816F | B1F | (DCIM) | ANCORAR | ANCORAR | 15KV_1F1(A) | ANCORAR | 15KV_1F1(A) | C10X600112,5KVAET4A112,5KVAS144-2 | V1-9 | M1M | ANCORAR | 112,5KVA | 37,5KVA112,5KVA112,5KVA | 50KVA | 37,5KVA112,5KVA112,5KVA | TX10 | MX | P1-11 | 35112,5KVA5M | Q/R | BF-A | P9 | 28M | FERRAGEM | 6G | FERRAGEM | 15KV_1L(C) | 5156KV5_81F62(B)112,5KVA | 15KV_1F1(A)</t>
+          <t>V1-2 | 1x3x120(70)AX | BT | MX | ANCORAR</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -886,7 +874,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P1-11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -894,7 +882,7 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>P9 | SOLICITANTE | ANCORAR | M1M | ENDERECO | Q/R | ANCORAR | (DCIM) | 15KV_1F1(A) | B1F | 37,5KVA112,5KVA112,5KVA</t>
+          <t>SOLICITANTE | M1M | Q/R | ENDERECO | ANCORAR | 15KV_1F1(A) | BAIRRO | 37112,5KVA112,5KVA | (DCIM) | ANCORAR | B1F</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -918,40 +906,36 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+          <t>V1-9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28m</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>P5 | CONEX. | P4-30 | C12X600112,5KVAB4A112,5KVABF-A | BT | BF-A | S143112,5KVA1AF(1) | 30K | 1x3x70(70)AX | 112,5KVA | 551412 | TX10 | TX10 | S145 | BF-A | C12X600112,5KVAB2F112,5KVAM3F | 21M | BF-A</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>15KV_1F1(A) | 550K8VA | C10X600112,5KVAET4A112,5KVAS144-2 | 37112,5KVAE5KTVA | 15KV_1F1(A) | 37112,5KVA112,5KVA | 2 | TX10 | M1M | (DCIM) | 400816F | BF-A | FERRAGEM | B1F | Q/R | 28M | 6G | 15KV_1L(C) | FERRAGEM | 5156KV5_81F62(B)112,5KVA | MX | 15KV_1F1(A)</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -967,32 +951,28 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VAO</t>
+          <t>POSTE</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>V4-5</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9.26m</t>
-        </is>
-      </c>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>V4-5 | 9.26M | 30K | 21M | 37M | BF-A</t>
+          <t>M1M | (DCIM) | 15KV_1F1(A) | B1F | ANCORAR | 15KV_1F1(A) | ANCORAR | 37112,5KVA112,5KVA | Q/R | 400816F | 37112,5KVAE5KTVA</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1021,7 +1001,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1037,7 +1017,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>P4-30 | CONEX. | 112,5KVA | S145 | TX10 | C12X600112,5KVAB2F112,5KVAM3F | BT | P5 | 14944166 | BF-A | 1x3x70(70)AX | BF-A | 21M | 400816F | TX10 | C10x300,B1M,SMTG | C12X600112,5KVAB4A112,5KVABF-A</t>
+          <t>CONEX. | BT | C12X600112,5KVAB4A112,5KVABF-A | BF-A | S143112,5KVA1AF(1) | 2 | 1x3x70(70)AX | 3 | TX10 | 551412 | TX10 | S145 | BF-A | C12X600112,5KVAB2F112,5KVAM3F | 21M | 14944166 | BF-A</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1065,36 +1045,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
+          <t>V4-5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9.26m</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>P31 | XX | GD | 4008661 | BT | (DCIM) | B1F | 112,5KVA | X63X51260(5708)A5X | B4F | C10X300112,5KVAS145 | ANCORAR | Q/R | 400816F | ANCORAR | ANCORAR | TX10 | 112,5KVA | CCO | 112,5KVA | BT | CABOS | AVENIDA | 112,5KVA | (DCIM) | BF-A | 84M | 112,5KVA | DCO</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>9.26M | 30K | 21M | 37M | 551412 | 1x3x70(70)AX | BF-A | BF-A</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1119,7 +1095,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1127,11 +1103,11 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>P2 | 175ET005296879 | 656529 | P1-11 | ETAPA | V1-2 | MX | 37,5KVA</t>
+          <t>(DCIM) | GD | 4008661 | B1F | BT | ANCORAR | ANCORAR | XX | 1 | BT | CABOS | 112,5KVA | AVENIDA | CCO</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1160,7 +1136,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>P1-11</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1176,11 +1152,11 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>MX | P1-11 | 112,5KVA | TX10 | 175ET005296879 | C10X600112,5KVAET4A112,5KVAS144-2 | 400816F | ANCORAR | BF-A | 50KVA | ANCORAR | 656529 | 28M | B1F | 15KV_1F1(A) | (DCIM) | 37,5KVA112,5KVA112,5KVA | 15KV_1F1(A) | V1-9 | 37,5KVA112,5KVA112,5KVA | FERRAGEM | ANCORAR | M1M | 15KV_1L(C) | 6G | V1-2 | 35112,5KVA5M | ANCORAR</t>
+          <t>XX | GD | 4008661 | BT | (DCIM) | B1F | 1 | X63X51260(5708)A5X | B4F | C10X300112,5KVAS145</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1209,23 +1185,23 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>V1-9</t>
+          <t>V2-3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28m</t>
+          <t>42.77M</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>400816F | B1F | (DCIM) | ANCORAR | ANCORAR | 15KV_1F1(A) | ANCORAR | 15KV_1F1(A) | C10X600112,5KVAET4A112,5KVAS144-2 | V1-9 | M1M | ANCORAR | 112,5KVA | 37,5KVA112,5KVA112,5KVA | 50KVA | 37,5KVA112,5KVA112,5KVA | TX10 | MX | P1-11 | 35112,5KVA5M | Q/R | BF-A | P9 | 28M | FERRAGEM | 6G | FERRAGEM | 15KV_1L(C) | 5156KV5_81F62(B)112,5KVA | 15KV_1F1(A)</t>
+          <t>X63X51260(5708)A5X | 1 | BT | V2-3</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1254,7 +1230,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1262,18 +1238,190 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>P9 | SOLICITANTE | ANCORAR | M1M | ENDERECO | Q/R | ANCORAR | (DCIM) | 15KV_1F1(A) | B1F | 37,5KVA112,5KVA112,5KVA</t>
+          <t>ETAPA | 7 | 175ET005296879 | 656529 | BF-A | 14944160 | BF-A</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>14944161</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>VAO</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>V1-2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32.2M</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>V1-2 | 1x3x120(70)AX | BT | MX | ANCORAR</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>14944161</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>POSTE</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>P1-11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>SOLICITANTE | M1M | Q/R | ENDERECO | ANCORAR | 15KV_1F1(A) | BAIRRO | 37112,5KVA112,5KVA | (DCIM) | ANCORAR | B1F</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>14944161</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>VAO</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>V1-9</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>28m</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>15KV_1F1(A) | 550K8VA | C10X600112,5KVAET4A112,5KVAS144-2 | 37112,5KVAE5KTVA | 15KV_1F1(A) | 37112,5KVA112,5KVA | 2 | TX10 | M1M | (DCIM) | 400816F | BF-A | FERRAGEM | B1F | Q/R | 28M | 6G | 15KV_1L(C) | FERRAGEM | 5156KV5_81F62(B)112,5KVA | MX | 15KV_1F1(A)</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>14944161</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>POSTE</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>M1M | (DCIM) | 15KV_1F1(A) | B1F | ANCORAR | 15KV_1F1(A) | ANCORAR | 37112,5KVA112,5KVA | Q/R | 400816F | 37112,5KVAE5KTVA</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>

--- a/output_excel/14944161.xlsx
+++ b/output_excel/14944161.xlsx
@@ -470,20 +470,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,35 +512,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rua / Avenida</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ancoragem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lado Forte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Metragem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Altura Poste</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Informações</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -563,30 +581,33 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | BT | C12X600112,5KVAB4A112,5KVABF-A | BF-A | S143112,5KVA1AF(1) | 2 | 1x3x70(70)AX | 3 | TX10 | 551412 | TX10 | S145 | BF-A | C12X600112,5KVAB2F112,5KVAM3F | 21M | 14944166 | BF-A</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>27.63m P5 C12X600112,5KVAB4A112,5KVABF-A | C12X600112,5KVAB2F112,5KVAM3F S145 | BF-A S143112,5KVA1AF(1) 551412 30K | CONEX. BT 1x3x70(70)AX | P4-30 2 TX10 | B4F C10X300112,5KVAS145</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -611,27 +632,30 @@
           <t>V4-5</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>9.26m</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>9.26M | 30K | 21M | 37M | 551412 | 1x3x70(70)AX | BF-A | BF-A</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n">
+          <t>9.26m</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>9.26M V4-5 | 2 V1-3 21M | 3 TX10 2 V1-3 37M | 8 TX10 2 V1-3 84M | BF-A S143112,5KVA1AF(1) 551412 30K | 4006551 | CONEX. BT 1x3x70(70)AX | 175ET005296879 656550</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -659,20 +683,31 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | GD | 4008661 | B1F | BT | ANCORAR | ANCORAR | XX | 1 | BT | CABOS | 112,5KVA | AVENIDA | CCO</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>B4F C10X300112,5KVAS145 | (DCIM) BT | P31 | XX | 112,5KVA CCO | 1 X63X51260(5708)A5X</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -698,30 +733,33 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>XX | GD | 4008661 | BT | (DCIM) | B1F | 1 | X63X51260(5708)A5X | B4F | C10X300112,5KVAS145</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>B4F C10X300112,5KVAS145 | P31 | XX | (DCIM) BT | C12X600112,5KVAB2F112,5KVAM3F S145 | 1 X63X51260(5708)A5X | Q/R</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -738,35 +776,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>VAO</t>
+          <t>POSTE</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>V2-3</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>42.77M</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>X63X51260(5708)A5X | 1 | BT | V2-3</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>400816F C10X600112,5KVAET4A112,5KVAS144-2 550K8VA CARGA 15KV_1L(C) | P2 | S144-2 C10X600112,5KVAB1M112,5KVAM3F | ETAPA 7 2 V1-3 14944160 | 175ET005296879 656529 | 112,5KVA 112,5KVA | P1-11 | BF-A 551392</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -788,26 +833,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1-11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>ETAPA | 7 | 175ET005296879 | 656529 | BF-A | 14944160 | BF-A</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>400816F C10X600112,5KVAET4A112,5KVAS144-2 550K8VA CARGA 15KV_1L(C) | P9 | SOLICITANTE | ENDERECO | BAIRRO | B1F (DCIM) 15KV_1F1(A) 15KV_1F1(A) 37112,5KVAE5KTVA 37112,5KVA112,5KVA 6G CARGA</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -829,30 +885,33 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>V1-2</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32.2M</t>
-        </is>
-      </c>
+          <t>V1-9</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>V1-2 | 1x3x120(70)AX | BT | MX | ANCORAR</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+          <t>28m</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>B1F (DCIM) 15KV_1F1(A) 15KV_1F1(A) 37112,5KVAE5KTVA 37112,5KVA112,5KVA 6G CARGA | 2 TX10 2 V1-3 28M | M1M Q/R | MX | V1-2 | (DCIM) | 5156KV5_81F62(B)112,5KVA15KV_1F1(A)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -874,26 +933,37 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>P1-11</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>SOLICITANTE | M1M | Q/R | ENDERECO | ANCORAR | 15KV_1F1(A) | BAIRRO | 37112,5KVA112,5KVA | (DCIM) | ANCORAR | B1F</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>400816F C10X600112,5KVAET4A112,5KVAS144-2 550K8VA CARGA 15KV_1L(C) | P9 | B1F (DCIM) 15KV_1F1(A) 15KV_1F1(A) 37112,5KVAE5KTVA 37112,5KVA112,5KVA 6G CARGA | 5156KV5_81F62(B)112,5KVA15KV_1F1(A) | P1-11</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -906,39 +976,46 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>VAO</t>
+          <t>POSTE</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>V1-9</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28m</t>
-        </is>
-      </c>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15KV_1F1(A) | 550K8VA | C10X600112,5KVAET4A112,5KVAS144-2 | 37112,5KVAE5KTVA | 15KV_1F1(A) | 37112,5KVA112,5KVA | 2 | TX10 | M1M | (DCIM) | 400816F | BF-A | FERRAGEM | B1F | Q/R | 28M | 6G | 15KV_1L(C) | FERRAGEM | 5156KV5_81F62(B)112,5KVA | MX | 15KV_1F1(A)</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27.63m P5 C12X600112,5KVAB4A112,5KVABF-A | C12X600112,5KVAB2F112,5KVAM3F S145 | BF-A S143112,5KVA1AF(1) 551412 30K | CONEX. BT 1x3x70(70)AX | P4-30 2 TX10 | B4F C10X300112,5KVAS145</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -951,16 +1028,16 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>V4-5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -968,18 +1045,25 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>M1M | (DCIM) | 15KV_1F1(A) | B1F | ANCORAR | 15KV_1F1(A) | ANCORAR | 37112,5KVA112,5KVA | Q/R | 400816F | 37112,5KVAE5KTVA</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+          <t>9.26m</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9.26M V4-5 | 2 V1-3 21M | 3 TX10 2 V1-3 37M | 8 TX10 2 V1-3 84M | BF-A S143112,5KVA1AF(1) 551412 30K | 4006551 | CONEX. BT 1x3x70(70)AX | 175ET005296879 656550</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1001,34 +1085,37 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | BT | C12X600112,5KVAB4A112,5KVABF-A | BF-A | S143112,5KVA1AF(1) | 2 | 1x3x70(70)AX | 3 | TX10 | 551412 | TX10 | S145 | BF-A | C12X600112,5KVAB2F112,5KVAM3F | 21M | 14944166 | BF-A</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>B4F C10X300112,5KVAS145 | (DCIM) BT | P31 | XX | 112,5KVA CCO | 1 X63X51260(5708)A5X</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1045,35 +1132,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VAO</t>
+          <t>POSTE</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>V4-5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9.26m</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9.26M | 30K | 21M | 37M | 551412 | 1x3x70(70)AX | BF-A | BF-A</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>B4F C10X300112,5KVAS145 | P31 | XX | (DCIM) BT | C12X600112,5KVAB2F112,5KVAM3F S145 | 1 X63X51260(5708)A5X | Q/R</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1095,26 +1189,37 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | GD | 4008661 | B1F | BT | ANCORAR | ANCORAR | XX | 1 | BT | CABOS | 112,5KVA | AVENIDA | CCO</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>400816F C10X600112,5KVAET4A112,5KVAS144-2 550K8VA CARGA 15KV_1L(C) | P2 | S144-2 C10X600112,5KVAB1M112,5KVAM3F | ETAPA 7 2 V1-3 14944160 | 175ET005296879 656529 | 112,5KVA 112,5KVA | P1-11 | BF-A 551392</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1136,34 +1241,37 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1-11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>XX | GD | 4008661 | BT | (DCIM) | B1F | 1 | X63X51260(5708)A5X | B4F | C10X300112,5KVAS145</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>400816F C10X600112,5KVAET4A112,5KVAS144-2 550K8VA CARGA 15KV_1L(C) | P9 | SOLICITANTE | ENDERECO | BAIRRO | B1F (DCIM) 15KV_1F1(A) 15KV_1F1(A) 37112,5KVAE5KTVA 37112,5KVA112,5KVA 6G CARGA</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1185,30 +1293,33 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>V2-3</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>42.77M</t>
-        </is>
-      </c>
+          <t>V1-9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>X63X51260(5708)A5X | 1 | BT | V2-3</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+          <t>28m</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>B1F (DCIM) 15KV_1F1(A) 15KV_1F1(A) 37112,5KVAE5KTVA 37112,5KVA112,5KVA 6G CARGA | 2 TX10 2 V1-3 28M | M1M Q/R | MX | V1-2 | (DCIM) | 5156KV5_81F62(B)112,5KVA15KV_1F1(A)</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1230,198 +1341,37 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>ETAPA | 7 | 175ET005296879 | 656529 | BF-A | 14944160 | BF-A</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>14944161</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>VAO</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>V1-2</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>32.2M</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>V1-2 | 1x3x120(70)AX | BT | MX | ANCORAR</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>14944161</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>POSTE</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>P1-11</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>SOLICITANTE | M1M | Q/R | ENDERECO | ANCORAR | 15KV_1F1(A) | BAIRRO | 37112,5KVA112,5KVA | (DCIM) | ANCORAR | B1F</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>14944161</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>VAO</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>V1-9</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>28m</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15KV_1F1(A) | 550K8VA | C10X600112,5KVAET4A112,5KVAS144-2 | 37112,5KVAE5KTVA | 15KV_1F1(A) | 37112,5KVA112,5KVA | 2 | TX10 | M1M | (DCIM) | 400816F | BF-A | FERRAGEM | B1F | Q/R | 28M | 6G | 15KV_1L(C) | FERRAGEM | 5156KV5_81F62(B)112,5KVA | MX | 15KV_1F1(A)</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>14944161</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>POSTE</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>M1M | (DCIM) | 15KV_1F1(A) | B1F | ANCORAR | 15KV_1F1(A) | ANCORAR | 37112,5KVA112,5KVA | Q/R | 400816F | 37112,5KVAE5KTVA</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
+          <t>400816F C10X600112,5KVAET4A112,5KVAS144-2 550K8VA CARGA 15KV_1L(C) | P9 | B1F (DCIM) 15KV_1F1(A) 15KV_1F1(A) 37112,5KVAE5KTVA 37112,5KVA112,5KVA 6G CARGA | 5156KV5_81F62(B)112,5KVA15KV_1F1(A) | P1-11</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
